--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2013/NEVADA_2013.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2013/NEVADA_2013.xlsx
@@ -3948,7 +3948,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C200">
@@ -13578,7 +13578,7 @@
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C735">
@@ -15018,7 +15018,7 @@
       </c>
       <c r="B815" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C815">
@@ -16332,7 +16332,7 @@
       </c>
       <c r="B888" t="inlineStr">
         <is>
-          <t>Santo Domingo Tonaltepec</t>
+          <t>Santo Domingo Tomaltepec</t>
         </is>
       </c>
       <c r="C888">
@@ -24180,7 +24180,7 @@
       </c>
       <c r="B1324" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C1324">
